--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_25-09-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_25-09-2025.xlsx
@@ -592,25 +592,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62e311eb5+80197]
-	GetHandleVerifier [0x0x7ff62e311f10+80288]
-	(No symbol) [0x0x7ff62e0902fa]
-	(No symbol) [0x0x7ff62e0e7cd7]
-	(No symbol) [0x0x7ff62e0e7f9c]
-	(No symbol) [0x0x7ff62e13ba87]
-	(No symbol) [0x0x7ff62e1103bf]
-	(No symbol) [0x0x7ff62e1387fb]
-	(No symbol) [0x0x7ff62e110153]
-	(No symbol) [0x0x7ff62e0d8b02]
-	(No symbol) [0x0x7ff62e0d98d3]
-	GetHandleVerifier [0x0x7ff62e5ce83d+2949837]
-	GetHandleVerifier [0x0x7ff62e5c8c6a+2926330]
-	GetHandleVerifier [0x0x7ff62e5e86c7+3055959]
-	GetHandleVerifier [0x0x7ff62e32cfee+191102]
-	GetHandleVerifier [0x0x7ff62e3350af+224063]
-	GetHandleVerifier [0x0x7ff62e31af64+117236]
-	GetHandleVerifier [0x0x7ff62e31b119+117673]
-	GetHandleVerifier [0x0x7ff62e3010a8+11064]
+	GetHandleVerifier [0x0x7ff689781eb5+80197]
+	GetHandleVerifier [0x0x7ff689781f10+80288]
+	(No symbol) [0x0x7ff6895002fa]
+	(No symbol) [0x0x7ff689557cd7]
+	(No symbol) [0x0x7ff689557f9c]
+	(No symbol) [0x0x7ff6895aba87]
+	(No symbol) [0x0x7ff6895803bf]
+	(No symbol) [0x0x7ff6895a87fb]
+	(No symbol) [0x0x7ff689580153]
+	(No symbol) [0x0x7ff689548b02]
+	(No symbol) [0x0x7ff6895498d3]
+	GetHandleVerifier [0x0x7ff689a3e83d+2949837]
+	GetHandleVerifier [0x0x7ff689a38c6a+2926330]
+	GetHandleVerifier [0x0x7ff689a586c7+3055959]
+	GetHandleVerifier [0x0x7ff68979cfee+191102]
+	GetHandleVerifier [0x0x7ff6897a50af+224063]
+	GetHandleVerifier [0x0x7ff68978af64+117236]
+	GetHandleVerifier [0x0x7ff68978b119+117673]
+	GetHandleVerifier [0x0x7ff6897710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -691,7 +691,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>£13.89</t>
+          <t>£11.99</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -714,25 +714,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62e311eb5+80197]
-	GetHandleVerifier [0x0x7ff62e311f10+80288]
-	(No symbol) [0x0x7ff62e0902fa]
-	(No symbol) [0x0x7ff62e0e7cd7]
-	(No symbol) [0x0x7ff62e0e7f9c]
-	(No symbol) [0x0x7ff62e13ba87]
-	(No symbol) [0x0x7ff62e1103bf]
-	(No symbol) [0x0x7ff62e1387fb]
-	(No symbol) [0x0x7ff62e110153]
-	(No symbol) [0x0x7ff62e0d8b02]
-	(No symbol) [0x0x7ff62e0d98d3]
-	GetHandleVerifier [0x0x7ff62e5ce83d+2949837]
-	GetHandleVerifier [0x0x7ff62e5c8c6a+2926330]
-	GetHandleVerifier [0x0x7ff62e5e86c7+3055959]
-	GetHandleVerifier [0x0x7ff62e32cfee+191102]
-	GetHandleVerifier [0x0x7ff62e3350af+224063]
-	GetHandleVerifier [0x0x7ff62e31af64+117236]
-	GetHandleVerifier [0x0x7ff62e31b119+117673]
-	GetHandleVerifier [0x0x7ff62e3010a8+11064]
+	GetHandleVerifier [0x0x7ff689781eb5+80197]
+	GetHandleVerifier [0x0x7ff689781f10+80288]
+	(No symbol) [0x0x7ff6895002fa]
+	(No symbol) [0x0x7ff689557cd7]
+	(No symbol) [0x0x7ff689557f9c]
+	(No symbol) [0x0x7ff6895aba87]
+	(No symbol) [0x0x7ff6895803bf]
+	(No symbol) [0x0x7ff6895a87fb]
+	(No symbol) [0x0x7ff689580153]
+	(No symbol) [0x0x7ff689548b02]
+	(No symbol) [0x0x7ff6895498d3]
+	GetHandleVerifier [0x0x7ff689a3e83d+2949837]
+	GetHandleVerifier [0x0x7ff689a38c6a+2926330]
+	GetHandleVerifier [0x0x7ff689a586c7+3055959]
+	GetHandleVerifier [0x0x7ff68979cfee+191102]
+	GetHandleVerifier [0x0x7ff6897a50af+224063]
+	GetHandleVerifier [0x0x7ff68978af64+117236]
+	GetHandleVerifier [0x0x7ff68978b119+117673]
+	GetHandleVerifier [0x0x7ff6897710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -813,7 +813,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>£16.88</t>
+          <t>£15.35</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -836,25 +836,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62e311eb5+80197]
-	GetHandleVerifier [0x0x7ff62e311f10+80288]
-	(No symbol) [0x0x7ff62e0902fa]
-	(No symbol) [0x0x7ff62e0e7cd7]
-	(No symbol) [0x0x7ff62e0e7f9c]
-	(No symbol) [0x0x7ff62e13ba87]
-	(No symbol) [0x0x7ff62e1103bf]
-	(No symbol) [0x0x7ff62e1387fb]
-	(No symbol) [0x0x7ff62e110153]
-	(No symbol) [0x0x7ff62e0d8b02]
-	(No symbol) [0x0x7ff62e0d98d3]
-	GetHandleVerifier [0x0x7ff62e5ce83d+2949837]
-	GetHandleVerifier [0x0x7ff62e5c8c6a+2926330]
-	GetHandleVerifier [0x0x7ff62e5e86c7+3055959]
-	GetHandleVerifier [0x0x7ff62e32cfee+191102]
-	GetHandleVerifier [0x0x7ff62e3350af+224063]
-	GetHandleVerifier [0x0x7ff62e31af64+117236]
-	GetHandleVerifier [0x0x7ff62e31b119+117673]
-	GetHandleVerifier [0x0x7ff62e3010a8+11064]
+	GetHandleVerifier [0x0x7ff689781eb5+80197]
+	GetHandleVerifier [0x0x7ff689781f10+80288]
+	(No symbol) [0x0x7ff6895002fa]
+	(No symbol) [0x0x7ff689557cd7]
+	(No symbol) [0x0x7ff689557f9c]
+	(No symbol) [0x0x7ff6895aba87]
+	(No symbol) [0x0x7ff6895803bf]
+	(No symbol) [0x0x7ff6895a87fb]
+	(No symbol) [0x0x7ff689580153]
+	(No symbol) [0x0x7ff689548b02]
+	(No symbol) [0x0x7ff6895498d3]
+	GetHandleVerifier [0x0x7ff689a3e83d+2949837]
+	GetHandleVerifier [0x0x7ff689a38c6a+2926330]
+	GetHandleVerifier [0x0x7ff689a586c7+3055959]
+	GetHandleVerifier [0x0x7ff68979cfee+191102]
+	GetHandleVerifier [0x0x7ff6897a50af+224063]
+	GetHandleVerifier [0x0x7ff68978af64+117236]
+	GetHandleVerifier [0x0x7ff68978b119+117673]
+	GetHandleVerifier [0x0x7ff6897710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -958,25 +958,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62e311eb5+80197]
-	GetHandleVerifier [0x0x7ff62e311f10+80288]
-	(No symbol) [0x0x7ff62e0902fa]
-	(No symbol) [0x0x7ff62e0e7cd7]
-	(No symbol) [0x0x7ff62e0e7f9c]
-	(No symbol) [0x0x7ff62e13ba87]
-	(No symbol) [0x0x7ff62e1103bf]
-	(No symbol) [0x0x7ff62e1387fb]
-	(No symbol) [0x0x7ff62e110153]
-	(No symbol) [0x0x7ff62e0d8b02]
-	(No symbol) [0x0x7ff62e0d98d3]
-	GetHandleVerifier [0x0x7ff62e5ce83d+2949837]
-	GetHandleVerifier [0x0x7ff62e5c8c6a+2926330]
-	GetHandleVerifier [0x0x7ff62e5e86c7+3055959]
-	GetHandleVerifier [0x0x7ff62e32cfee+191102]
-	GetHandleVerifier [0x0x7ff62e3350af+224063]
-	GetHandleVerifier [0x0x7ff62e31af64+117236]
-	GetHandleVerifier [0x0x7ff62e31b119+117673]
-	GetHandleVerifier [0x0x7ff62e3010a8+11064]
+	GetHandleVerifier [0x0x7ff689781eb5+80197]
+	GetHandleVerifier [0x0x7ff689781f10+80288]
+	(No symbol) [0x0x7ff6895002fa]
+	(No symbol) [0x0x7ff689557cd7]
+	(No symbol) [0x0x7ff689557f9c]
+	(No symbol) [0x0x7ff6895aba87]
+	(No symbol) [0x0x7ff6895803bf]
+	(No symbol) [0x0x7ff6895a87fb]
+	(No symbol) [0x0x7ff689580153]
+	(No symbol) [0x0x7ff689548b02]
+	(No symbol) [0x0x7ff6895498d3]
+	GetHandleVerifier [0x0x7ff689a3e83d+2949837]
+	GetHandleVerifier [0x0x7ff689a38c6a+2926330]
+	GetHandleVerifier [0x0x7ff689a586c7+3055959]
+	GetHandleVerifier [0x0x7ff68979cfee+191102]
+	GetHandleVerifier [0x0x7ff6897a50af+224063]
+	GetHandleVerifier [0x0x7ff68978af64+117236]
+	GetHandleVerifier [0x0x7ff68978b119+117673]
+	GetHandleVerifier [0x0x7ff6897710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1080,25 +1080,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62e311eb5+80197]
-	GetHandleVerifier [0x0x7ff62e311f10+80288]
-	(No symbol) [0x0x7ff62e0902fa]
-	(No symbol) [0x0x7ff62e0e7cd7]
-	(No symbol) [0x0x7ff62e0e7f9c]
-	(No symbol) [0x0x7ff62e13ba87]
-	(No symbol) [0x0x7ff62e1103bf]
-	(No symbol) [0x0x7ff62e1387fb]
-	(No symbol) [0x0x7ff62e110153]
-	(No symbol) [0x0x7ff62e0d8b02]
-	(No symbol) [0x0x7ff62e0d98d3]
-	GetHandleVerifier [0x0x7ff62e5ce83d+2949837]
-	GetHandleVerifier [0x0x7ff62e5c8c6a+2926330]
-	GetHandleVerifier [0x0x7ff62e5e86c7+3055959]
-	GetHandleVerifier [0x0x7ff62e32cfee+191102]
-	GetHandleVerifier [0x0x7ff62e3350af+224063]
-	GetHandleVerifier [0x0x7ff62e31af64+117236]
-	GetHandleVerifier [0x0x7ff62e31b119+117673]
-	GetHandleVerifier [0x0x7ff62e3010a8+11064]
+	GetHandleVerifier [0x0x7ff689781eb5+80197]
+	GetHandleVerifier [0x0x7ff689781f10+80288]
+	(No symbol) [0x0x7ff6895002fa]
+	(No symbol) [0x0x7ff689557cd7]
+	(No symbol) [0x0x7ff689557f9c]
+	(No symbol) [0x0x7ff6895aba87]
+	(No symbol) [0x0x7ff6895803bf]
+	(No symbol) [0x0x7ff6895a87fb]
+	(No symbol) [0x0x7ff689580153]
+	(No symbol) [0x0x7ff689548b02]
+	(No symbol) [0x0x7ff6895498d3]
+	GetHandleVerifier [0x0x7ff689a3e83d+2949837]
+	GetHandleVerifier [0x0x7ff689a38c6a+2926330]
+	GetHandleVerifier [0x0x7ff689a586c7+3055959]
+	GetHandleVerifier [0x0x7ff68979cfee+191102]
+	GetHandleVerifier [0x0x7ff6897a50af+224063]
+	GetHandleVerifier [0x0x7ff68978af64+117236]
+	GetHandleVerifier [0x0x7ff68978b119+117673]
+	GetHandleVerifier [0x0x7ff6897710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1202,25 +1202,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62e311eb5+80197]
-	GetHandleVerifier [0x0x7ff62e311f10+80288]
-	(No symbol) [0x0x7ff62e0902fa]
-	(No symbol) [0x0x7ff62e0e7cd7]
-	(No symbol) [0x0x7ff62e0e7f9c]
-	(No symbol) [0x0x7ff62e13ba87]
-	(No symbol) [0x0x7ff62e1103bf]
-	(No symbol) [0x0x7ff62e1387fb]
-	(No symbol) [0x0x7ff62e110153]
-	(No symbol) [0x0x7ff62e0d8b02]
-	(No symbol) [0x0x7ff62e0d98d3]
-	GetHandleVerifier [0x0x7ff62e5ce83d+2949837]
-	GetHandleVerifier [0x0x7ff62e5c8c6a+2926330]
-	GetHandleVerifier [0x0x7ff62e5e86c7+3055959]
-	GetHandleVerifier [0x0x7ff62e32cfee+191102]
-	GetHandleVerifier [0x0x7ff62e3350af+224063]
-	GetHandleVerifier [0x0x7ff62e31af64+117236]
-	GetHandleVerifier [0x0x7ff62e31b119+117673]
-	GetHandleVerifier [0x0x7ff62e3010a8+11064]
+	GetHandleVerifier [0x0x7ff689781eb5+80197]
+	GetHandleVerifier [0x0x7ff689781f10+80288]
+	(No symbol) [0x0x7ff6895002fa]
+	(No symbol) [0x0x7ff689557cd7]
+	(No symbol) [0x0x7ff689557f9c]
+	(No symbol) [0x0x7ff6895aba87]
+	(No symbol) [0x0x7ff6895803bf]
+	(No symbol) [0x0x7ff6895a87fb]
+	(No symbol) [0x0x7ff689580153]
+	(No symbol) [0x0x7ff689548b02]
+	(No symbol) [0x0x7ff6895498d3]
+	GetHandleVerifier [0x0x7ff689a3e83d+2949837]
+	GetHandleVerifier [0x0x7ff689a38c6a+2926330]
+	GetHandleVerifier [0x0x7ff689a586c7+3055959]
+	GetHandleVerifier [0x0x7ff68979cfee+191102]
+	GetHandleVerifier [0x0x7ff6897a50af+224063]
+	GetHandleVerifier [0x0x7ff68978af64+117236]
+	GetHandleVerifier [0x0x7ff68978b119+117673]
+	GetHandleVerifier [0x0x7ff6897710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1324,25 +1324,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62e311eb5+80197]
-	GetHandleVerifier [0x0x7ff62e311f10+80288]
-	(No symbol) [0x0x7ff62e0902fa]
-	(No symbol) [0x0x7ff62e0e7cd7]
-	(No symbol) [0x0x7ff62e0e7f9c]
-	(No symbol) [0x0x7ff62e13ba87]
-	(No symbol) [0x0x7ff62e1103bf]
-	(No symbol) [0x0x7ff62e1387fb]
-	(No symbol) [0x0x7ff62e110153]
-	(No symbol) [0x0x7ff62e0d8b02]
-	(No symbol) [0x0x7ff62e0d98d3]
-	GetHandleVerifier [0x0x7ff62e5ce83d+2949837]
-	GetHandleVerifier [0x0x7ff62e5c8c6a+2926330]
-	GetHandleVerifier [0x0x7ff62e5e86c7+3055959]
-	GetHandleVerifier [0x0x7ff62e32cfee+191102]
-	GetHandleVerifier [0x0x7ff62e3350af+224063]
-	GetHandleVerifier [0x0x7ff62e31af64+117236]
-	GetHandleVerifier [0x0x7ff62e31b119+117673]
-	GetHandleVerifier [0x0x7ff62e3010a8+11064]
+	GetHandleVerifier [0x0x7ff689781eb5+80197]
+	GetHandleVerifier [0x0x7ff689781f10+80288]
+	(No symbol) [0x0x7ff6895002fa]
+	(No symbol) [0x0x7ff689557cd7]
+	(No symbol) [0x0x7ff689557f9c]
+	(No symbol) [0x0x7ff6895aba87]
+	(No symbol) [0x0x7ff6895803bf]
+	(No symbol) [0x0x7ff6895a87fb]
+	(No symbol) [0x0x7ff689580153]
+	(No symbol) [0x0x7ff689548b02]
+	(No symbol) [0x0x7ff6895498d3]
+	GetHandleVerifier [0x0x7ff689a3e83d+2949837]
+	GetHandleVerifier [0x0x7ff689a38c6a+2926330]
+	GetHandleVerifier [0x0x7ff689a586c7+3055959]
+	GetHandleVerifier [0x0x7ff68979cfee+191102]
+	GetHandleVerifier [0x0x7ff6897a50af+224063]
+	GetHandleVerifier [0x0x7ff68978af64+117236]
+	GetHandleVerifier [0x0x7ff68978b119+117673]
+	GetHandleVerifier [0x0x7ff6897710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1446,25 +1446,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62e311eb5+80197]
-	GetHandleVerifier [0x0x7ff62e311f10+80288]
-	(No symbol) [0x0x7ff62e0902fa]
-	(No symbol) [0x0x7ff62e0e7cd7]
-	(No symbol) [0x0x7ff62e0e7f9c]
-	(No symbol) [0x0x7ff62e13ba87]
-	(No symbol) [0x0x7ff62e1103bf]
-	(No symbol) [0x0x7ff62e1387fb]
-	(No symbol) [0x0x7ff62e110153]
-	(No symbol) [0x0x7ff62e0d8b02]
-	(No symbol) [0x0x7ff62e0d98d3]
-	GetHandleVerifier [0x0x7ff62e5ce83d+2949837]
-	GetHandleVerifier [0x0x7ff62e5c8c6a+2926330]
-	GetHandleVerifier [0x0x7ff62e5e86c7+3055959]
-	GetHandleVerifier [0x0x7ff62e32cfee+191102]
-	GetHandleVerifier [0x0x7ff62e3350af+224063]
-	GetHandleVerifier [0x0x7ff62e31af64+117236]
-	GetHandleVerifier [0x0x7ff62e31b119+117673]
-	GetHandleVerifier [0x0x7ff62e3010a8+11064]
+	GetHandleVerifier [0x0x7ff689781eb5+80197]
+	GetHandleVerifier [0x0x7ff689781f10+80288]
+	(No symbol) [0x0x7ff6895002fa]
+	(No symbol) [0x0x7ff689557cd7]
+	(No symbol) [0x0x7ff689557f9c]
+	(No symbol) [0x0x7ff6895aba87]
+	(No symbol) [0x0x7ff6895803bf]
+	(No symbol) [0x0x7ff6895a87fb]
+	(No symbol) [0x0x7ff689580153]
+	(No symbol) [0x0x7ff689548b02]
+	(No symbol) [0x0x7ff6895498d3]
+	GetHandleVerifier [0x0x7ff689a3e83d+2949837]
+	GetHandleVerifier [0x0x7ff689a38c6a+2926330]
+	GetHandleVerifier [0x0x7ff689a586c7+3055959]
+	GetHandleVerifier [0x0x7ff68979cfee+191102]
+	GetHandleVerifier [0x0x7ff6897a50af+224063]
+	GetHandleVerifier [0x0x7ff68978af64+117236]
+	GetHandleVerifier [0x0x7ff68978b119+117673]
+	GetHandleVerifier [0x0x7ff6897710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>£27.33</t>
+          <t>£27.30</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1568,25 +1568,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62e311eb5+80197]
-	GetHandleVerifier [0x0x7ff62e311f10+80288]
-	(No symbol) [0x0x7ff62e0902fa]
-	(No symbol) [0x0x7ff62e0e7cd7]
-	(No symbol) [0x0x7ff62e0e7f9c]
-	(No symbol) [0x0x7ff62e13ba87]
-	(No symbol) [0x0x7ff62e1103bf]
-	(No symbol) [0x0x7ff62e1387fb]
-	(No symbol) [0x0x7ff62e110153]
-	(No symbol) [0x0x7ff62e0d8b02]
-	(No symbol) [0x0x7ff62e0d98d3]
-	GetHandleVerifier [0x0x7ff62e5ce83d+2949837]
-	GetHandleVerifier [0x0x7ff62e5c8c6a+2926330]
-	GetHandleVerifier [0x0x7ff62e5e86c7+3055959]
-	GetHandleVerifier [0x0x7ff62e32cfee+191102]
-	GetHandleVerifier [0x0x7ff62e3350af+224063]
-	GetHandleVerifier [0x0x7ff62e31af64+117236]
-	GetHandleVerifier [0x0x7ff62e31b119+117673]
-	GetHandleVerifier [0x0x7ff62e3010a8+11064]
+	GetHandleVerifier [0x0x7ff689781eb5+80197]
+	GetHandleVerifier [0x0x7ff689781f10+80288]
+	(No symbol) [0x0x7ff6895002fa]
+	(No symbol) [0x0x7ff689557cd7]
+	(No symbol) [0x0x7ff689557f9c]
+	(No symbol) [0x0x7ff6895aba87]
+	(No symbol) [0x0x7ff6895803bf]
+	(No symbol) [0x0x7ff6895a87fb]
+	(No symbol) [0x0x7ff689580153]
+	(No symbol) [0x0x7ff689548b02]
+	(No symbol) [0x0x7ff6895498d3]
+	GetHandleVerifier [0x0x7ff689a3e83d+2949837]
+	GetHandleVerifier [0x0x7ff689a38c6a+2926330]
+	GetHandleVerifier [0x0x7ff689a586c7+3055959]
+	GetHandleVerifier [0x0x7ff68979cfee+191102]
+	GetHandleVerifier [0x0x7ff6897a50af+224063]
+	GetHandleVerifier [0x0x7ff68978af64+117236]
+	GetHandleVerifier [0x0x7ff68978b119+117673]
+	GetHandleVerifier [0x0x7ff6897710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1690,25 +1690,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62e311eb5+80197]
-	GetHandleVerifier [0x0x7ff62e311f10+80288]
-	(No symbol) [0x0x7ff62e0902fa]
-	(No symbol) [0x0x7ff62e0e7cd7]
-	(No symbol) [0x0x7ff62e0e7f9c]
-	(No symbol) [0x0x7ff62e13ba87]
-	(No symbol) [0x0x7ff62e1103bf]
-	(No symbol) [0x0x7ff62e1387fb]
-	(No symbol) [0x0x7ff62e110153]
-	(No symbol) [0x0x7ff62e0d8b02]
-	(No symbol) [0x0x7ff62e0d98d3]
-	GetHandleVerifier [0x0x7ff62e5ce83d+2949837]
-	GetHandleVerifier [0x0x7ff62e5c8c6a+2926330]
-	GetHandleVerifier [0x0x7ff62e5e86c7+3055959]
-	GetHandleVerifier [0x0x7ff62e32cfee+191102]
-	GetHandleVerifier [0x0x7ff62e3350af+224063]
-	GetHandleVerifier [0x0x7ff62e31af64+117236]
-	GetHandleVerifier [0x0x7ff62e31b119+117673]
-	GetHandleVerifier [0x0x7ff62e3010a8+11064]
+	GetHandleVerifier [0x0x7ff689781eb5+80197]
+	GetHandleVerifier [0x0x7ff689781f10+80288]
+	(No symbol) [0x0x7ff6895002fa]
+	(No symbol) [0x0x7ff689557cd7]
+	(No symbol) [0x0x7ff689557f9c]
+	(No symbol) [0x0x7ff6895aba87]
+	(No symbol) [0x0x7ff6895803bf]
+	(No symbol) [0x0x7ff6895a87fb]
+	(No symbol) [0x0x7ff689580153]
+	(No symbol) [0x0x7ff689548b02]
+	(No symbol) [0x0x7ff6895498d3]
+	GetHandleVerifier [0x0x7ff689a3e83d+2949837]
+	GetHandleVerifier [0x0x7ff689a38c6a+2926330]
+	GetHandleVerifier [0x0x7ff689a586c7+3055959]
+	GetHandleVerifier [0x0x7ff68979cfee+191102]
+	GetHandleVerifier [0x0x7ff6897a50af+224063]
+	GetHandleVerifier [0x0x7ff68978af64+117236]
+	GetHandleVerifier [0x0x7ff68978b119+117673]
+	GetHandleVerifier [0x0x7ff6897710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>£35.57</t>
+          <t>£35.56</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1812,25 +1812,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62e311eb5+80197]
-	GetHandleVerifier [0x0x7ff62e311f10+80288]
-	(No symbol) [0x0x7ff62e0902fa]
-	(No symbol) [0x0x7ff62e0e7cd7]
-	(No symbol) [0x0x7ff62e0e7f9c]
-	(No symbol) [0x0x7ff62e13ba87]
-	(No symbol) [0x0x7ff62e1103bf]
-	(No symbol) [0x0x7ff62e1387fb]
-	(No symbol) [0x0x7ff62e110153]
-	(No symbol) [0x0x7ff62e0d8b02]
-	(No symbol) [0x0x7ff62e0d98d3]
-	GetHandleVerifier [0x0x7ff62e5ce83d+2949837]
-	GetHandleVerifier [0x0x7ff62e5c8c6a+2926330]
-	GetHandleVerifier [0x0x7ff62e5e86c7+3055959]
-	GetHandleVerifier [0x0x7ff62e32cfee+191102]
-	GetHandleVerifier [0x0x7ff62e3350af+224063]
-	GetHandleVerifier [0x0x7ff62e31af64+117236]
-	GetHandleVerifier [0x0x7ff62e31b119+117673]
-	GetHandleVerifier [0x0x7ff62e3010a8+11064]
+	GetHandleVerifier [0x0x7ff689781eb5+80197]
+	GetHandleVerifier [0x0x7ff689781f10+80288]
+	(No symbol) [0x0x7ff6895002fa]
+	(No symbol) [0x0x7ff689557cd7]
+	(No symbol) [0x0x7ff689557f9c]
+	(No symbol) [0x0x7ff6895aba87]
+	(No symbol) [0x0x7ff6895803bf]
+	(No symbol) [0x0x7ff6895a87fb]
+	(No symbol) [0x0x7ff689580153]
+	(No symbol) [0x0x7ff689548b02]
+	(No symbol) [0x0x7ff6895498d3]
+	GetHandleVerifier [0x0x7ff689a3e83d+2949837]
+	GetHandleVerifier [0x0x7ff689a38c6a+2926330]
+	GetHandleVerifier [0x0x7ff689a586c7+3055959]
+	GetHandleVerifier [0x0x7ff68979cfee+191102]
+	GetHandleVerifier [0x0x7ff6897a50af+224063]
+	GetHandleVerifier [0x0x7ff68978af64+117236]
+	GetHandleVerifier [0x0x7ff68978b119+117673]
+	GetHandleVerifier [0x0x7ff6897710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1934,25 +1934,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62e311eb5+80197]
-	GetHandleVerifier [0x0x7ff62e311f10+80288]
-	(No symbol) [0x0x7ff62e0902fa]
-	(No symbol) [0x0x7ff62e0e7cd7]
-	(No symbol) [0x0x7ff62e0e7f9c]
-	(No symbol) [0x0x7ff62e13ba87]
-	(No symbol) [0x0x7ff62e1103bf]
-	(No symbol) [0x0x7ff62e1387fb]
-	(No symbol) [0x0x7ff62e110153]
-	(No symbol) [0x0x7ff62e0d8b02]
-	(No symbol) [0x0x7ff62e0d98d3]
-	GetHandleVerifier [0x0x7ff62e5ce83d+2949837]
-	GetHandleVerifier [0x0x7ff62e5c8c6a+2926330]
-	GetHandleVerifier [0x0x7ff62e5e86c7+3055959]
-	GetHandleVerifier [0x0x7ff62e32cfee+191102]
-	GetHandleVerifier [0x0x7ff62e3350af+224063]
-	GetHandleVerifier [0x0x7ff62e31af64+117236]
-	GetHandleVerifier [0x0x7ff62e31b119+117673]
-	GetHandleVerifier [0x0x7ff62e3010a8+11064]
+	GetHandleVerifier [0x0x7ff689781eb5+80197]
+	GetHandleVerifier [0x0x7ff689781f10+80288]
+	(No symbol) [0x0x7ff6895002fa]
+	(No symbol) [0x0x7ff689557cd7]
+	(No symbol) [0x0x7ff689557f9c]
+	(No symbol) [0x0x7ff6895aba87]
+	(No symbol) [0x0x7ff6895803bf]
+	(No symbol) [0x0x7ff6895a87fb]
+	(No symbol) [0x0x7ff689580153]
+	(No symbol) [0x0x7ff689548b02]
+	(No symbol) [0x0x7ff6895498d3]
+	GetHandleVerifier [0x0x7ff689a3e83d+2949837]
+	GetHandleVerifier [0x0x7ff689a38c6a+2926330]
+	GetHandleVerifier [0x0x7ff689a586c7+3055959]
+	GetHandleVerifier [0x0x7ff68979cfee+191102]
+	GetHandleVerifier [0x0x7ff6897a50af+224063]
+	GetHandleVerifier [0x0x7ff68978af64+117236]
+	GetHandleVerifier [0x0x7ff68978b119+117673]
+	GetHandleVerifier [0x0x7ff6897710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2056,25 +2056,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62e311eb5+80197]
-	GetHandleVerifier [0x0x7ff62e311f10+80288]
-	(No symbol) [0x0x7ff62e0902fa]
-	(No symbol) [0x0x7ff62e0e7cd7]
-	(No symbol) [0x0x7ff62e0e7f9c]
-	(No symbol) [0x0x7ff62e13ba87]
-	(No symbol) [0x0x7ff62e1103bf]
-	(No symbol) [0x0x7ff62e1387fb]
-	(No symbol) [0x0x7ff62e110153]
-	(No symbol) [0x0x7ff62e0d8b02]
-	(No symbol) [0x0x7ff62e0d98d3]
-	GetHandleVerifier [0x0x7ff62e5ce83d+2949837]
-	GetHandleVerifier [0x0x7ff62e5c8c6a+2926330]
-	GetHandleVerifier [0x0x7ff62e5e86c7+3055959]
-	GetHandleVerifier [0x0x7ff62e32cfee+191102]
-	GetHandleVerifier [0x0x7ff62e3350af+224063]
-	GetHandleVerifier [0x0x7ff62e31af64+117236]
-	GetHandleVerifier [0x0x7ff62e31b119+117673]
-	GetHandleVerifier [0x0x7ff62e3010a8+11064]
+	GetHandleVerifier [0x0x7ff689781eb5+80197]
+	GetHandleVerifier [0x0x7ff689781f10+80288]
+	(No symbol) [0x0x7ff6895002fa]
+	(No symbol) [0x0x7ff689557cd7]
+	(No symbol) [0x0x7ff689557f9c]
+	(No symbol) [0x0x7ff6895aba87]
+	(No symbol) [0x0x7ff6895803bf]
+	(No symbol) [0x0x7ff6895a87fb]
+	(No symbol) [0x0x7ff689580153]
+	(No symbol) [0x0x7ff689548b02]
+	(No symbol) [0x0x7ff6895498d3]
+	GetHandleVerifier [0x0x7ff689a3e83d+2949837]
+	GetHandleVerifier [0x0x7ff689a38c6a+2926330]
+	GetHandleVerifier [0x0x7ff689a586c7+3055959]
+	GetHandleVerifier [0x0x7ff68979cfee+191102]
+	GetHandleVerifier [0x0x7ff6897a50af+224063]
+	GetHandleVerifier [0x0x7ff68978af64+117236]
+	GetHandleVerifier [0x0x7ff68978b119+117673]
+	GetHandleVerifier [0x0x7ff6897710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2177,25 +2177,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62e311eb5+80197]
-	GetHandleVerifier [0x0x7ff62e311f10+80288]
-	(No symbol) [0x0x7ff62e0902fa]
-	(No symbol) [0x0x7ff62e0e7cd7]
-	(No symbol) [0x0x7ff62e0e7f9c]
-	(No symbol) [0x0x7ff62e13ba87]
-	(No symbol) [0x0x7ff62e1103bf]
-	(No symbol) [0x0x7ff62e1387fb]
-	(No symbol) [0x0x7ff62e110153]
-	(No symbol) [0x0x7ff62e0d8b02]
-	(No symbol) [0x0x7ff62e0d98d3]
-	GetHandleVerifier [0x0x7ff62e5ce83d+2949837]
-	GetHandleVerifier [0x0x7ff62e5c8c6a+2926330]
-	GetHandleVerifier [0x0x7ff62e5e86c7+3055959]
-	GetHandleVerifier [0x0x7ff62e32cfee+191102]
-	GetHandleVerifier [0x0x7ff62e3350af+224063]
-	GetHandleVerifier [0x0x7ff62e31af64+117236]
-	GetHandleVerifier [0x0x7ff62e31b119+117673]
-	GetHandleVerifier [0x0x7ff62e3010a8+11064]
+	GetHandleVerifier [0x0x7ff689781eb5+80197]
+	GetHandleVerifier [0x0x7ff689781f10+80288]
+	(No symbol) [0x0x7ff6895002fa]
+	(No symbol) [0x0x7ff689557cd7]
+	(No symbol) [0x0x7ff689557f9c]
+	(No symbol) [0x0x7ff6895aba87]
+	(No symbol) [0x0x7ff6895803bf]
+	(No symbol) [0x0x7ff6895a87fb]
+	(No symbol) [0x0x7ff689580153]
+	(No symbol) [0x0x7ff689548b02]
+	(No symbol) [0x0x7ff6895498d3]
+	GetHandleVerifier [0x0x7ff689a3e83d+2949837]
+	GetHandleVerifier [0x0x7ff689a38c6a+2926330]
+	GetHandleVerifier [0x0x7ff689a586c7+3055959]
+	GetHandleVerifier [0x0x7ff68979cfee+191102]
+	GetHandleVerifier [0x0x7ff6897a50af+224063]
+	GetHandleVerifier [0x0x7ff68978af64+117236]
+	GetHandleVerifier [0x0x7ff68978b119+117673]
+	GetHandleVerifier [0x0x7ff6897710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2299,25 +2299,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62e311eb5+80197]
-	GetHandleVerifier [0x0x7ff62e311f10+80288]
-	(No symbol) [0x0x7ff62e0902fa]
-	(No symbol) [0x0x7ff62e0e7cd7]
-	(No symbol) [0x0x7ff62e0e7f9c]
-	(No symbol) [0x0x7ff62e13ba87]
-	(No symbol) [0x0x7ff62e1103bf]
-	(No symbol) [0x0x7ff62e1387fb]
-	(No symbol) [0x0x7ff62e110153]
-	(No symbol) [0x0x7ff62e0d8b02]
-	(No symbol) [0x0x7ff62e0d98d3]
-	GetHandleVerifier [0x0x7ff62e5ce83d+2949837]
-	GetHandleVerifier [0x0x7ff62e5c8c6a+2926330]
-	GetHandleVerifier [0x0x7ff62e5e86c7+3055959]
-	GetHandleVerifier [0x0x7ff62e32cfee+191102]
-	GetHandleVerifier [0x0x7ff62e3350af+224063]
-	GetHandleVerifier [0x0x7ff62e31af64+117236]
-	GetHandleVerifier [0x0x7ff62e31b119+117673]
-	GetHandleVerifier [0x0x7ff62e3010a8+11064]
+	GetHandleVerifier [0x0x7ff689781eb5+80197]
+	GetHandleVerifier [0x0x7ff689781f10+80288]
+	(No symbol) [0x0x7ff6895002fa]
+	(No symbol) [0x0x7ff689557cd7]
+	(No symbol) [0x0x7ff689557f9c]
+	(No symbol) [0x0x7ff6895aba87]
+	(No symbol) [0x0x7ff6895803bf]
+	(No symbol) [0x0x7ff6895a87fb]
+	(No symbol) [0x0x7ff689580153]
+	(No symbol) [0x0x7ff689548b02]
+	(No symbol) [0x0x7ff6895498d3]
+	GetHandleVerifier [0x0x7ff689a3e83d+2949837]
+	GetHandleVerifier [0x0x7ff689a38c6a+2926330]
+	GetHandleVerifier [0x0x7ff689a586c7+3055959]
+	GetHandleVerifier [0x0x7ff68979cfee+191102]
+	GetHandleVerifier [0x0x7ff6897a50af+224063]
+	GetHandleVerifier [0x0x7ff68978af64+117236]
+	GetHandleVerifier [0x0x7ff68978b119+117673]
+	GetHandleVerifier [0x0x7ff6897710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2519,25 +2519,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62e311eb5+80197]
-	GetHandleVerifier [0x0x7ff62e311f10+80288]
-	(No symbol) [0x0x7ff62e0902fa]
-	(No symbol) [0x0x7ff62e0e7cd7]
-	(No symbol) [0x0x7ff62e0e7f9c]
-	(No symbol) [0x0x7ff62e13ba87]
-	(No symbol) [0x0x7ff62e1103bf]
-	(No symbol) [0x0x7ff62e1387fb]
-	(No symbol) [0x0x7ff62e110153]
-	(No symbol) [0x0x7ff62e0d8b02]
-	(No symbol) [0x0x7ff62e0d98d3]
-	GetHandleVerifier [0x0x7ff62e5ce83d+2949837]
-	GetHandleVerifier [0x0x7ff62e5c8c6a+2926330]
-	GetHandleVerifier [0x0x7ff62e5e86c7+3055959]
-	GetHandleVerifier [0x0x7ff62e32cfee+191102]
-	GetHandleVerifier [0x0x7ff62e3350af+224063]
-	GetHandleVerifier [0x0x7ff62e31af64+117236]
-	GetHandleVerifier [0x0x7ff62e31b119+117673]
-	GetHandleVerifier [0x0x7ff62e3010a8+11064]
+	GetHandleVerifier [0x0x7ff689781eb5+80197]
+	GetHandleVerifier [0x0x7ff689781f10+80288]
+	(No symbol) [0x0x7ff6895002fa]
+	(No symbol) [0x0x7ff689557cd7]
+	(No symbol) [0x0x7ff689557f9c]
+	(No symbol) [0x0x7ff6895aba87]
+	(No symbol) [0x0x7ff6895803bf]
+	(No symbol) [0x0x7ff6895a87fb]
+	(No symbol) [0x0x7ff689580153]
+	(No symbol) [0x0x7ff689548b02]
+	(No symbol) [0x0x7ff6895498d3]
+	GetHandleVerifier [0x0x7ff689a3e83d+2949837]
+	GetHandleVerifier [0x0x7ff689a38c6a+2926330]
+	GetHandleVerifier [0x0x7ff689a586c7+3055959]
+	GetHandleVerifier [0x0x7ff68979cfee+191102]
+	GetHandleVerifier [0x0x7ff6897a50af+224063]
+	GetHandleVerifier [0x0x7ff68978af64+117236]
+	GetHandleVerifier [0x0x7ff68978b119+117673]
+	GetHandleVerifier [0x0x7ff6897710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2640,25 +2640,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62e311eb5+80197]
-	GetHandleVerifier [0x0x7ff62e311f10+80288]
-	(No symbol) [0x0x7ff62e0902fa]
-	(No symbol) [0x0x7ff62e0e7cd7]
-	(No symbol) [0x0x7ff62e0e7f9c]
-	(No symbol) [0x0x7ff62e13ba87]
-	(No symbol) [0x0x7ff62e1103bf]
-	(No symbol) [0x0x7ff62e1387fb]
-	(No symbol) [0x0x7ff62e110153]
-	(No symbol) [0x0x7ff62e0d8b02]
-	(No symbol) [0x0x7ff62e0d98d3]
-	GetHandleVerifier [0x0x7ff62e5ce83d+2949837]
-	GetHandleVerifier [0x0x7ff62e5c8c6a+2926330]
-	GetHandleVerifier [0x0x7ff62e5e86c7+3055959]
-	GetHandleVerifier [0x0x7ff62e32cfee+191102]
-	GetHandleVerifier [0x0x7ff62e3350af+224063]
-	GetHandleVerifier [0x0x7ff62e31af64+117236]
-	GetHandleVerifier [0x0x7ff62e31b119+117673]
-	GetHandleVerifier [0x0x7ff62e3010a8+11064]
+	GetHandleVerifier [0x0x7ff689781eb5+80197]
+	GetHandleVerifier [0x0x7ff689781f10+80288]
+	(No symbol) [0x0x7ff6895002fa]
+	(No symbol) [0x0x7ff689557cd7]
+	(No symbol) [0x0x7ff689557f9c]
+	(No symbol) [0x0x7ff6895aba87]
+	(No symbol) [0x0x7ff6895803bf]
+	(No symbol) [0x0x7ff6895a87fb]
+	(No symbol) [0x0x7ff689580153]
+	(No symbol) [0x0x7ff689548b02]
+	(No symbol) [0x0x7ff6895498d3]
+	GetHandleVerifier [0x0x7ff689a3e83d+2949837]
+	GetHandleVerifier [0x0x7ff689a38c6a+2926330]
+	GetHandleVerifier [0x0x7ff689a586c7+3055959]
+	GetHandleVerifier [0x0x7ff68979cfee+191102]
+	GetHandleVerifier [0x0x7ff6897a50af+224063]
+	GetHandleVerifier [0x0x7ff68978af64+117236]
+	GetHandleVerifier [0x0x7ff68978b119+117673]
+	GetHandleVerifier [0x0x7ff6897710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2761,25 +2761,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62e311eb5+80197]
-	GetHandleVerifier [0x0x7ff62e311f10+80288]
-	(No symbol) [0x0x7ff62e0902fa]
-	(No symbol) [0x0x7ff62e0e7cd7]
-	(No symbol) [0x0x7ff62e0e7f9c]
-	(No symbol) [0x0x7ff62e13ba87]
-	(No symbol) [0x0x7ff62e1103bf]
-	(No symbol) [0x0x7ff62e1387fb]
-	(No symbol) [0x0x7ff62e110153]
-	(No symbol) [0x0x7ff62e0d8b02]
-	(No symbol) [0x0x7ff62e0d98d3]
-	GetHandleVerifier [0x0x7ff62e5ce83d+2949837]
-	GetHandleVerifier [0x0x7ff62e5c8c6a+2926330]
-	GetHandleVerifier [0x0x7ff62e5e86c7+3055959]
-	GetHandleVerifier [0x0x7ff62e32cfee+191102]
-	GetHandleVerifier [0x0x7ff62e3350af+224063]
-	GetHandleVerifier [0x0x7ff62e31af64+117236]
-	GetHandleVerifier [0x0x7ff62e31b119+117673]
-	GetHandleVerifier [0x0x7ff62e3010a8+11064]
+	GetHandleVerifier [0x0x7ff689781eb5+80197]
+	GetHandleVerifier [0x0x7ff689781f10+80288]
+	(No symbol) [0x0x7ff6895002fa]
+	(No symbol) [0x0x7ff689557cd7]
+	(No symbol) [0x0x7ff689557f9c]
+	(No symbol) [0x0x7ff6895aba87]
+	(No symbol) [0x0x7ff6895803bf]
+	(No symbol) [0x0x7ff6895a87fb]
+	(No symbol) [0x0x7ff689580153]
+	(No symbol) [0x0x7ff689548b02]
+	(No symbol) [0x0x7ff6895498d3]
+	GetHandleVerifier [0x0x7ff689a3e83d+2949837]
+	GetHandleVerifier [0x0x7ff689a38c6a+2926330]
+	GetHandleVerifier [0x0x7ff689a586c7+3055959]
+	GetHandleVerifier [0x0x7ff68979cfee+191102]
+	GetHandleVerifier [0x0x7ff6897a50af+224063]
+	GetHandleVerifier [0x0x7ff68978af64+117236]
+	GetHandleVerifier [0x0x7ff68978b119+117673]
+	GetHandleVerifier [0x0x7ff6897710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2882,25 +2882,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62e311eb5+80197]
-	GetHandleVerifier [0x0x7ff62e311f10+80288]
-	(No symbol) [0x0x7ff62e0902fa]
-	(No symbol) [0x0x7ff62e0e7cd7]
-	(No symbol) [0x0x7ff62e0e7f9c]
-	(No symbol) [0x0x7ff62e13ba87]
-	(No symbol) [0x0x7ff62e1103bf]
-	(No symbol) [0x0x7ff62e1387fb]
-	(No symbol) [0x0x7ff62e110153]
-	(No symbol) [0x0x7ff62e0d8b02]
-	(No symbol) [0x0x7ff62e0d98d3]
-	GetHandleVerifier [0x0x7ff62e5ce83d+2949837]
-	GetHandleVerifier [0x0x7ff62e5c8c6a+2926330]
-	GetHandleVerifier [0x0x7ff62e5e86c7+3055959]
-	GetHandleVerifier [0x0x7ff62e32cfee+191102]
-	GetHandleVerifier [0x0x7ff62e3350af+224063]
-	GetHandleVerifier [0x0x7ff62e31af64+117236]
-	GetHandleVerifier [0x0x7ff62e31b119+117673]
-	GetHandleVerifier [0x0x7ff62e3010a8+11064]
+	GetHandleVerifier [0x0x7ff689781eb5+80197]
+	GetHandleVerifier [0x0x7ff689781f10+80288]
+	(No symbol) [0x0x7ff6895002fa]
+	(No symbol) [0x0x7ff689557cd7]
+	(No symbol) [0x0x7ff689557f9c]
+	(No symbol) [0x0x7ff6895aba87]
+	(No symbol) [0x0x7ff6895803bf]
+	(No symbol) [0x0x7ff6895a87fb]
+	(No symbol) [0x0x7ff689580153]
+	(No symbol) [0x0x7ff689548b02]
+	(No symbol) [0x0x7ff6895498d3]
+	GetHandleVerifier [0x0x7ff689a3e83d+2949837]
+	GetHandleVerifier [0x0x7ff689a38c6a+2926330]
+	GetHandleVerifier [0x0x7ff689a586c7+3055959]
+	GetHandleVerifier [0x0x7ff68979cfee+191102]
+	GetHandleVerifier [0x0x7ff6897a50af+224063]
+	GetHandleVerifier [0x0x7ff68978af64+117236]
+	GetHandleVerifier [0x0x7ff68978b119+117673]
+	GetHandleVerifier [0x0x7ff6897710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -3003,25 +3003,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62e311eb5+80197]
-	GetHandleVerifier [0x0x7ff62e311f10+80288]
-	(No symbol) [0x0x7ff62e0902fa]
-	(No symbol) [0x0x7ff62e0e7cd7]
-	(No symbol) [0x0x7ff62e0e7f9c]
-	(No symbol) [0x0x7ff62e13ba87]
-	(No symbol) [0x0x7ff62e1103bf]
-	(No symbol) [0x0x7ff62e1387fb]
-	(No symbol) [0x0x7ff62e110153]
-	(No symbol) [0x0x7ff62e0d8b02]
-	(No symbol) [0x0x7ff62e0d98d3]
-	GetHandleVerifier [0x0x7ff62e5ce83d+2949837]
-	GetHandleVerifier [0x0x7ff62e5c8c6a+2926330]
-	GetHandleVerifier [0x0x7ff62e5e86c7+3055959]
-	GetHandleVerifier [0x0x7ff62e32cfee+191102]
-	GetHandleVerifier [0x0x7ff62e3350af+224063]
-	GetHandleVerifier [0x0x7ff62e31af64+117236]
-	GetHandleVerifier [0x0x7ff62e31b119+117673]
-	GetHandleVerifier [0x0x7ff62e3010a8+11064]
+	GetHandleVerifier [0x0x7ff689781eb5+80197]
+	GetHandleVerifier [0x0x7ff689781f10+80288]
+	(No symbol) [0x0x7ff6895002fa]
+	(No symbol) [0x0x7ff689557cd7]
+	(No symbol) [0x0x7ff689557f9c]
+	(No symbol) [0x0x7ff6895aba87]
+	(No symbol) [0x0x7ff6895803bf]
+	(No symbol) [0x0x7ff6895a87fb]
+	(No symbol) [0x0x7ff689580153]
+	(No symbol) [0x0x7ff689548b02]
+	(No symbol) [0x0x7ff6895498d3]
+	GetHandleVerifier [0x0x7ff689a3e83d+2949837]
+	GetHandleVerifier [0x0x7ff689a38c6a+2926330]
+	GetHandleVerifier [0x0x7ff689a586c7+3055959]
+	GetHandleVerifier [0x0x7ff68979cfee+191102]
+	GetHandleVerifier [0x0x7ff6897a50af+224063]
+	GetHandleVerifier [0x0x7ff68978af64+117236]
+	GetHandleVerifier [0x0x7ff68978b119+117673]
+	GetHandleVerifier [0x0x7ff6897710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -3124,25 +3124,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62e311eb5+80197]
-	GetHandleVerifier [0x0x7ff62e311f10+80288]
-	(No symbol) [0x0x7ff62e0902fa]
-	(No symbol) [0x0x7ff62e0e7cd7]
-	(No symbol) [0x0x7ff62e0e7f9c]
-	(No symbol) [0x0x7ff62e13ba87]
-	(No symbol) [0x0x7ff62e1103bf]
-	(No symbol) [0x0x7ff62e1387fb]
-	(No symbol) [0x0x7ff62e110153]
-	(No symbol) [0x0x7ff62e0d8b02]
-	(No symbol) [0x0x7ff62e0d98d3]
-	GetHandleVerifier [0x0x7ff62e5ce83d+2949837]
-	GetHandleVerifier [0x0x7ff62e5c8c6a+2926330]
-	GetHandleVerifier [0x0x7ff62e5e86c7+3055959]
-	GetHandleVerifier [0x0x7ff62e32cfee+191102]
-	GetHandleVerifier [0x0x7ff62e3350af+224063]
-	GetHandleVerifier [0x0x7ff62e31af64+117236]
-	GetHandleVerifier [0x0x7ff62e31b119+117673]
-	GetHandleVerifier [0x0x7ff62e3010a8+11064]
+	GetHandleVerifier [0x0x7ff689781eb5+80197]
+	GetHandleVerifier [0x0x7ff689781f10+80288]
+	(No symbol) [0x0x7ff6895002fa]
+	(No symbol) [0x0x7ff689557cd7]
+	(No symbol) [0x0x7ff689557f9c]
+	(No symbol) [0x0x7ff6895aba87]
+	(No symbol) [0x0x7ff6895803bf]
+	(No symbol) [0x0x7ff6895a87fb]
+	(No symbol) [0x0x7ff689580153]
+	(No symbol) [0x0x7ff689548b02]
+	(No symbol) [0x0x7ff6895498d3]
+	GetHandleVerifier [0x0x7ff689a3e83d+2949837]
+	GetHandleVerifier [0x0x7ff689a38c6a+2926330]
+	GetHandleVerifier [0x0x7ff689a586c7+3055959]
+	GetHandleVerifier [0x0x7ff68979cfee+191102]
+	GetHandleVerifier [0x0x7ff6897a50af+224063]
+	GetHandleVerifier [0x0x7ff68978af64+117236]
+	GetHandleVerifier [0x0x7ff68978b119+117673]
+	GetHandleVerifier [0x0x7ff6897710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -3245,25 +3245,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62e311eb5+80197]
-	GetHandleVerifier [0x0x7ff62e311f10+80288]
-	(No symbol) [0x0x7ff62e0902fa]
-	(No symbol) [0x0x7ff62e0e7cd7]
-	(No symbol) [0x0x7ff62e0e7f9c]
-	(No symbol) [0x0x7ff62e13ba87]
-	(No symbol) [0x0x7ff62e1103bf]
-	(No symbol) [0x0x7ff62e1387fb]
-	(No symbol) [0x0x7ff62e110153]
-	(No symbol) [0x0x7ff62e0d8b02]
-	(No symbol) [0x0x7ff62e0d98d3]
-	GetHandleVerifier [0x0x7ff62e5ce83d+2949837]
-	GetHandleVerifier [0x0x7ff62e5c8c6a+2926330]
-	GetHandleVerifier [0x0x7ff62e5e86c7+3055959]
-	GetHandleVerifier [0x0x7ff62e32cfee+191102]
-	GetHandleVerifier [0x0x7ff62e3350af+224063]
-	GetHandleVerifier [0x0x7ff62e31af64+117236]
-	GetHandleVerifier [0x0x7ff62e31b119+117673]
-	GetHandleVerifier [0x0x7ff62e3010a8+11064]
+	GetHandleVerifier [0x0x7ff689781eb5+80197]
+	GetHandleVerifier [0x0x7ff689781f10+80288]
+	(No symbol) [0x0x7ff6895002fa]
+	(No symbol) [0x0x7ff689557cd7]
+	(No symbol) [0x0x7ff689557f9c]
+	(No symbol) [0x0x7ff6895aba87]
+	(No symbol) [0x0x7ff6895803bf]
+	(No symbol) [0x0x7ff6895a87fb]
+	(No symbol) [0x0x7ff689580153]
+	(No symbol) [0x0x7ff689548b02]
+	(No symbol) [0x0x7ff6895498d3]
+	GetHandleVerifier [0x0x7ff689a3e83d+2949837]
+	GetHandleVerifier [0x0x7ff689a38c6a+2926330]
+	GetHandleVerifier [0x0x7ff689a586c7+3055959]
+	GetHandleVerifier [0x0x7ff68979cfee+191102]
+	GetHandleVerifier [0x0x7ff6897a50af+224063]
+	GetHandleVerifier [0x0x7ff68978af64+117236]
+	GetHandleVerifier [0x0x7ff68978b119+117673]
+	GetHandleVerifier [0x0x7ff6897710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -3366,25 +3366,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62e311eb5+80197]
-	GetHandleVerifier [0x0x7ff62e311f10+80288]
-	(No symbol) [0x0x7ff62e0902fa]
-	(No symbol) [0x0x7ff62e0e7cd7]
-	(No symbol) [0x0x7ff62e0e7f9c]
-	(No symbol) [0x0x7ff62e13ba87]
-	(No symbol) [0x0x7ff62e1103bf]
-	(No symbol) [0x0x7ff62e1387fb]
-	(No symbol) [0x0x7ff62e110153]
-	(No symbol) [0x0x7ff62e0d8b02]
-	(No symbol) [0x0x7ff62e0d98d3]
-	GetHandleVerifier [0x0x7ff62e5ce83d+2949837]
-	GetHandleVerifier [0x0x7ff62e5c8c6a+2926330]
-	GetHandleVerifier [0x0x7ff62e5e86c7+3055959]
-	GetHandleVerifier [0x0x7ff62e32cfee+191102]
-	GetHandleVerifier [0x0x7ff62e3350af+224063]
-	GetHandleVerifier [0x0x7ff62e31af64+117236]
-	GetHandleVerifier [0x0x7ff62e31b119+117673]
-	GetHandleVerifier [0x0x7ff62e3010a8+11064]
+	GetHandleVerifier [0x0x7ff689781eb5+80197]
+	GetHandleVerifier [0x0x7ff689781f10+80288]
+	(No symbol) [0x0x7ff6895002fa]
+	(No symbol) [0x0x7ff689557cd7]
+	(No symbol) [0x0x7ff689557f9c]
+	(No symbol) [0x0x7ff6895aba87]
+	(No symbol) [0x0x7ff6895803bf]
+	(No symbol) [0x0x7ff6895a87fb]
+	(No symbol) [0x0x7ff689580153]
+	(No symbol) [0x0x7ff689548b02]
+	(No symbol) [0x0x7ff6895498d3]
+	GetHandleVerifier [0x0x7ff689a3e83d+2949837]
+	GetHandleVerifier [0x0x7ff689a38c6a+2926330]
+	GetHandleVerifier [0x0x7ff689a586c7+3055959]
+	GetHandleVerifier [0x0x7ff68979cfee+191102]
+	GetHandleVerifier [0x0x7ff6897a50af+224063]
+	GetHandleVerifier [0x0x7ff68978af64+117236]
+	GetHandleVerifier [0x0x7ff68978b119+117673]
+	GetHandleVerifier [0x0x7ff6897710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -3487,25 +3487,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62e311eb5+80197]
-	GetHandleVerifier [0x0x7ff62e311f10+80288]
-	(No symbol) [0x0x7ff62e0902fa]
-	(No symbol) [0x0x7ff62e0e7cd7]
-	(No symbol) [0x0x7ff62e0e7f9c]
-	(No symbol) [0x0x7ff62e13ba87]
-	(No symbol) [0x0x7ff62e1103bf]
-	(No symbol) [0x0x7ff62e1387fb]
-	(No symbol) [0x0x7ff62e110153]
-	(No symbol) [0x0x7ff62e0d8b02]
-	(No symbol) [0x0x7ff62e0d98d3]
-	GetHandleVerifier [0x0x7ff62e5ce83d+2949837]
-	GetHandleVerifier [0x0x7ff62e5c8c6a+2926330]
-	GetHandleVerifier [0x0x7ff62e5e86c7+3055959]
-	GetHandleVerifier [0x0x7ff62e32cfee+191102]
-	GetHandleVerifier [0x0x7ff62e3350af+224063]
-	GetHandleVerifier [0x0x7ff62e31af64+117236]
-	GetHandleVerifier [0x0x7ff62e31b119+117673]
-	GetHandleVerifier [0x0x7ff62e3010a8+11064]
+	GetHandleVerifier [0x0x7ff689781eb5+80197]
+	GetHandleVerifier [0x0x7ff689781f10+80288]
+	(No symbol) [0x0x7ff6895002fa]
+	(No symbol) [0x0x7ff689557cd7]
+	(No symbol) [0x0x7ff689557f9c]
+	(No symbol) [0x0x7ff6895aba87]
+	(No symbol) [0x0x7ff6895803bf]
+	(No symbol) [0x0x7ff6895a87fb]
+	(No symbol) [0x0x7ff689580153]
+	(No symbol) [0x0x7ff689548b02]
+	(No symbol) [0x0x7ff6895498d3]
+	GetHandleVerifier [0x0x7ff689a3e83d+2949837]
+	GetHandleVerifier [0x0x7ff689a38c6a+2926330]
+	GetHandleVerifier [0x0x7ff689a586c7+3055959]
+	GetHandleVerifier [0x0x7ff68979cfee+191102]
+	GetHandleVerifier [0x0x7ff6897a50af+224063]
+	GetHandleVerifier [0x0x7ff68978af64+117236]
+	GetHandleVerifier [0x0x7ff68978b119+117673]
+	GetHandleVerifier [0x0x7ff6897710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
